--- a/Result/profitability/7711.xlsx
+++ b/Result/profitability/7711.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM14"/>
+  <dimension ref="A1:AM15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1741,10 +1741,10 @@
         <v>205</v>
       </c>
       <c r="L11" t="n">
-        <v>3.39</v>
+        <v>3.28</v>
       </c>
       <c r="M11" t="n">
-        <v>1.8875</v>
+        <v>1.87375</v>
       </c>
       <c r="N11" t="n">
         <v>18.36875</v>
@@ -1774,10 +1774,10 @@
         <v>114.2</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1499999999999999</v>
+        <v>0.03999999999999959</v>
       </c>
       <c r="X11" t="n">
-        <v>0.04629629629629628</v>
+        <v>0.01234567901234551</v>
       </c>
       <c r="Y11" t="n">
         <v>-3.369999999999999</v>
@@ -1786,10 +1786,10 @@
         <v>-0.3333333333333333</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.5066666666666668</v>
+        <v>0.4577777777777776</v>
       </c>
       <c r="AC11" t="n">
         <v>-17.04</v>
@@ -1871,7 +1871,7 @@
         <v>2.67</v>
       </c>
       <c r="M12" t="n">
-        <v>2.43375</v>
+        <v>2.42</v>
       </c>
       <c r="N12" t="n">
         <v>16.55125</v>
@@ -1901,10 +1901,10 @@
         <v>114.3</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.7200000000000002</v>
+        <v>-0.6099999999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2123893805309734</v>
+        <v>-0.1859756097560975</v>
       </c>
       <c r="Y12" t="n">
         <v>0.6899999999999995</v>
@@ -1998,7 +1998,7 @@
         <v>3.92</v>
       </c>
       <c r="M13" t="n">
-        <v>2.6975</v>
+        <v>2.68375</v>
       </c>
       <c r="N13" t="n">
         <v>14.1575</v>
@@ -2125,7 +2125,7 @@
         <v>7.68</v>
       </c>
       <c r="M14" t="n">
-        <v>3.60125</v>
+        <v>3.5875</v>
       </c>
       <c r="N14" t="n">
         <v>12.565</v>
@@ -2206,6 +2206,133 @@
       </c>
       <c r="AM14" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>7711</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>6820</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5528</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1292</v>
+      </c>
+      <c r="F15" t="n">
+        <v>18.94</v>
+      </c>
+      <c r="G15" t="n">
+        <v>818</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>11.99%</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>813</v>
+      </c>
+      <c r="K15" t="n">
+        <v>685</v>
+      </c>
+      <c r="L15" t="n">
+        <v>9.76</v>
+      </c>
+      <c r="M15" t="n">
+        <v>4.52625</v>
+      </c>
+      <c r="N15" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.2708333333333333</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>6.550000000000001</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.5286521388216303</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.975609756097561</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.810089020771513</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK15" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
